--- a/05 experimento/DEF CON 22/03 procesados/05 - todos a 10.5.1.2/ataques empleados.xlsx
+++ b/05 experimento/DEF CON 22/03 procesados/05 - todos a 10.5.1.2/ataques empleados.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Tesis-Ciberataque\desarrollo\05 experimento\DEF CON 22\03 procesados\05 - todos a 10.5.1.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{EB6BDBA6-056A-4E80-AF8A-C64EA1E8E9F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5442EC0-69DB-4804-AC4C-740B611DDDA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ataques empleados" sheetId="1" r:id="rId1"/>
@@ -173,7 +173,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -310,7 +310,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -490,8 +490,14 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -606,6 +612,174 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -651,12 +825,47 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -702,7 +911,36 @@
     <cellStyle name="Título 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="5">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -713,6 +951,19 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{17808BC3-8B12-4127-9AAF-89E2083FC97F}" name="Tabla1" displayName="Tabla1" ref="A1:D1048576" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="3" tableBorderDxfId="4">
+  <autoFilter ref="A1:D1048576" xr:uid="{17808BC3-8B12-4127-9AAF-89E2083FC97F}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{10FAA876-D402-4915-B36F-098CC95583D6}" name="SID"/>
+    <tableColumn id="2" xr3:uid="{D5B6B0B5-BDC2-4970-86DB-4729204DDCA9}" name="Etapa"/>
+    <tableColumn id="3" xr3:uid="{61E65014-FEF0-4FBD-8911-500668749FA0}" name="Tipo" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{ACE43364-9AFE-4855-8B1D-F4DD5C18DF81}" name="Alerta" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1011,7 +1262,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1431,425 +1682,430 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="22.77734375" customWidth="1"/>
-    <col min="4" max="4" width="159.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.21875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" ht="23.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2">
+      <c r="D1" s="19" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="12">
         <v>366</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" s="13">
+        <v>1</v>
+      </c>
+      <c r="C2" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="15" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3">
+    <row r="3" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <v>368</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4">
+    <row r="4" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <v>384</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5">
+    <row r="5" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <v>469</v>
       </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B5" s="2">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6">
+    <row r="6" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <v>382</v>
       </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B6" s="2">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7">
+    <row r="7" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <v>381</v>
       </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B7" s="2">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8">
+    <row r="8" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <v>1333</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="2">
         <v>2</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9">
+    <row r="9" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <v>2664</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="2">
         <v>2</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10">
+    <row r="10" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <v>474</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="2">
         <v>2</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
+    <row r="11" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="7">
         <v>100000122</v>
       </c>
-      <c r="B11">
-        <v>3</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="B11" s="2">
+        <v>3</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12">
+    <row r="12" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
         <v>1421</v>
       </c>
-      <c r="B12">
-        <v>3</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="B12" s="2">
+        <v>3</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13">
+    <row r="13" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
         <v>249</v>
       </c>
-      <c r="B13">
-        <v>3</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="B13" s="2">
+        <v>3</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14">
+    <row r="14" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
         <v>1420</v>
       </c>
-      <c r="B14">
-        <v>3</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="B14" s="2">
+        <v>3</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15">
+    <row r="15" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
         <v>1418</v>
       </c>
-      <c r="B15">
-        <v>3</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="B15" s="2">
+        <v>3</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16">
+    <row r="16" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
         <v>100000210</v>
       </c>
-      <c r="B16">
-        <v>3</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="B16" s="2">
+        <v>3</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17">
+    <row r="17" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
         <v>1087</v>
       </c>
-      <c r="B17">
-        <v>3</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="B17" s="2">
+        <v>3</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18">
+    <row r="18" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
         <v>1122</v>
       </c>
-      <c r="B18">
-        <v>3</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B18" s="2">
+        <v>3</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19">
+    <row r="19" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
         <v>1372</v>
       </c>
-      <c r="B19">
-        <v>3</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="B19" s="2">
+        <v>3</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A20">
+    <row r="20" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
         <v>1325</v>
       </c>
-      <c r="B20">
-        <v>3</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="B20" s="2">
+        <v>3</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A21">
+    <row r="21" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
         <v>2118</v>
       </c>
-      <c r="B21">
-        <v>3</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="B21" s="2">
+        <v>3</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A22">
+    <row r="22" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
         <v>3072</v>
       </c>
-      <c r="B22">
-        <v>3</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="B22" s="2">
+        <v>3</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A23">
+    <row r="23" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A23" s="5">
         <v>3069</v>
       </c>
-      <c r="B23">
-        <v>3</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="B23" s="2">
+        <v>3</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24">
+    <row r="24" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="5">
         <v>1113</v>
       </c>
-      <c r="B24">
-        <v>3</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="B24" s="2">
+        <v>3</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A25">
+    <row r="25" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="5">
         <v>3007</v>
       </c>
-      <c r="B25">
-        <v>3</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="B25" s="2">
+        <v>3</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26">
+    <row r="26" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A26" s="5">
         <v>2273</v>
       </c>
-      <c r="B26">
-        <v>3</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="B26" s="2">
+        <v>3</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27">
+    <row r="27" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A27" s="5">
         <v>1336</v>
       </c>
-      <c r="B27">
-        <v>3</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="B27" s="2">
+        <v>3</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A28">
+    <row r="28" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A28" s="5">
         <v>3065</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="2">
         <v>4</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29">
+    <row r="29" spans="1:4" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="8">
         <v>160</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="9">
         <v>4</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" s="11" t="s">
         <v>30</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:F1"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D29">
     <sortCondition ref="B2:B29"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>